--- a/data_extactor/batch_10_fa/trimmed/batch_0050_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0050_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | ریاضیات | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | کارشناسان خون‌گیری (فلبوتومیست‌ها) | تکنسین‌های اتاق عمل | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی</t>
+          <t>کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های خون‌گیری | تکنسین‌های اتاق عمل | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | وضوح گفتار | حساسیت به مسئله | درک کتبی | چابکی انگشتان</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | وضوح گفتار | حساسیت به مسئله | درک کتبی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دستیاران پزشک (Medical Assistants) | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | تکنسین‌های اتاق عمل</t>
+          <t>کمک‌پزشکان و دستیاران مطب | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | پزشکی و دندانپزشکی | مدیریت و امور اداری | آموزش و تدریس | درمان و مشاوره‌</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | پزشکی و دندان‌پزشکی | مدیریت و اداره | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | مراقبان سلامت در منزل | دستیاران پزشک (Medical Assistants) | کمک‌بهیاران | امدادگران و تکنسین‌های اورژانس (Paramedics) | پرستاران دارای پروانه (RN)</t>
+          <t>پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | مراقبان سلامت و بهیاران مراقبت در منزل | کمک‌پزشکان و دستیاران مطب | کمک‌پرستاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پرستاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | حقوق و مقررات دولتی | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان مدیریت اسناد و مدارک | بایگان‌ها و کارمندان پرونده‌ها | کارشناسان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت سرطان و داده‌های بالینی | منشی‌ها و دستیاران اداری پزشکی | پیاده‌سازان متون پزشکی (ترانسکریپشنیست‌ها) | نمایندگان امور مراجعان و بیماران</t>
+          <t>کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | پیاده‌سازان و تایپیست‌های متون پزشکی | کارشناسان امور بیماران و پذیرش</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | ریاضیات | تولید و فراوری | امور اداری و دفتری | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | تولید و فرآوری | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | استدلال قیاسی | چابکی انگشتان | ثبات دست و بازو</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | استدلال قیاسی | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان تجویز و ساخت سمعک | تکنسین‌های آزمایشگاه و کارگاه ساخت عدسی | تکنسین‌های مراقبت‌های چشمی | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | تکنسین‌های داروخانه</t>
+          <t>کارشناسان تجویز و ساخت سمعک | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | تکنسین‌های مراقبت‌های چشمی | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | تکنسین‌های داروخانه (نسخه‌پیچ‌ها)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | طراحی | درمان و مشاوره‌ | مکانیک | تولید و فراوری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | طراحی | درمان و مشاوره | مکانیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | تجسم فضایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های ساخت پروتز و تجهیزات پزشکی | بهیاران و کمک‌های کاردرمانی | جراحان ارتوپدی (بزرگسالان) | پزشکان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | متخصصان طب پا (پودیاتریست‌ها) | متخصصان پروتزهای دندانی (پروستودنتیست‌ها)</t>
+          <t>تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | کمک‌یاران کاردرمانی | جراحان ارتوپدی، غیر از اطفال | متخصصان طب فیزیکی و توانبخشی | فیزیوتراپیست‌ها | پزشکان متخصص پا و مچ پا | متخصصان پروتزهای دندانی (پروستودنتیست‌ها)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش | تفکر انتقادی | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | درمان و مشاوره‌ | پزشکی و دندانپزشکی | رایانه و الکترونیک | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | درمان و مشاوره | پزشکی و دندان‌پزشکی | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>شنوایی‌شناسان (ادیولوژیست‌ها) | دستیاران پزشک (Medical Assistants) | تکنسین‌های مراقبت‌های چشمی | بینایی‌سنج‌ها (اپتومتریست‌ها) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | گفتاردرمانگران (پاتولوژیست‌های گفتار و زبان) | دستیاران گفتاردرمانی</t>
+          <t>شنوایی‌شناسان | کمک‌پزشکان و دستیاران مطب | تکنسین‌های مراقبت‌های چشمی | بینایی‌سنج‌ها (اپتومتریست‌ها) | ارتوپدهای فنی و سازندگان اعضای مصنوعی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | شیمی | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | شیمی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنسین‌ها و کارشناسان قلب و عروق | کارشناسان سونوگرافی تشخیصی | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | تکنسین‌های اتاق عمل | تکنسین‌های داروخانه | کارشناسان خون‌گیری (فلبوتومیست‌ها)</t>
+          <t>کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | تکنسین‌های اتاق عمل | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | کارشناسان و تکنسین‌های خون‌گیری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | پزشکی و دندانپزشکی | زیست‌شناسی | روان‌شناسی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان قلب و عروق | کارشناسان سونوگرافی تشخیصی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان آزمایشگاه پزشکی و بالینی | کارشناسان پزشکی هسته‌ای | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | تکنسین‌های اتاق عمل</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندانپزشکی | زبان انگلیسی | آموزش و تدریس | ریاضیات | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | چابکی انگشتان</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | وضوح گفتار | درک کتبی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان سونوگرافی تشخیصی | دستیاران پزشک (Medical Assistants) | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های مراقبت‌های چشمی | متخصصان چشم‌پزشکی (بزرگسالان) | بینایی‌سنج‌ها (اپتومتریست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری</t>
+          <t>سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کمک‌پزشکان و دستیاران مطب | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های مراقبت‌های چشمی | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
